--- a/7_Sinif_Haftalik_Ders_Calisma_Programi.xlsx
+++ b/7_Sinif_Haftalik_Ders_Calisma_Programi.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Nasıl Düzenlenir" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Haftalik Program'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Haftalik Program'!$A$1:$H$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,49 +56,65 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3B57"/>
-      <sz val="9"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0037474F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A237E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00BF360C"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="000D47A1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00BF360C"/>
-      <sz val="9"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001B5E20"/>
-      <sz val="9"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="004A148C"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0037474F"/>
-      <sz val="9"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00827717"/>
-      <sz val="9"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00004D40"/>
-      <sz val="9"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00311B92"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -114,6 +130,29 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3B57"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0037474F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A237E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00455A64"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00BF360C"/>
       <sz val="10"/>
     </font>
@@ -135,12 +174,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00455A64"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00827717"/>
       <sz val="10"/>
     </font>
@@ -148,6 +181,18 @@
       <name val="Arial"/>
       <color rgb="0000695C"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00311B92"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00546E7A"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -175,7 +220,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -214,8 +259,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
-        <bgColor rgb="00BBDEFB"/>
+        <fgColor rgb="00CFD8DC"/>
+        <bgColor rgb="00CFD8DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B3C7E6"/>
+        <bgColor rgb="00B3C7E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -226,6 +277,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C8E6C9"/>
         <bgColor rgb="00C8E6C9"/>
       </patternFill>
@@ -256,8 +313,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CFCFEA"/>
+        <bgColor rgb="00CFCFEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F3B57"/>
         <bgColor rgb="001F3B57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F7FA"/>
+        <bgColor rgb="00F5F7FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -287,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -326,51 +395,80 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -739,10 +837,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -777,7 +875,7 @@
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Rehber Öğretmen: Merve Çelik</t>
+          <t>Rehber Öğretmen: Merve Çelik   |   Program: 17:30 Okul Çıkışı – 22:00 Uyku</t>
         </is>
       </c>
       <c r="C2" s="6" t="n"/>
@@ -805,553 +903,745 @@
       <c r="G3" s="8" t="n"/>
       <c r="H3" s="8" t="n"/>
     </row>
-    <row r="4" ht="26" customHeight="1">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Renk Kodları:</t>
+          <t>Renk
+Kodları:</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
+          <t>Giriş / Dinlenme</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Günlük Ödev</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Matematik</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
           <t>Türkçe</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Matematik</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>Fen Bilimleri</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>Sosyal Bilgiler</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>Mola</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>Yemek / Serbest</t>
-        </is>
-      </c>
-      <c r="H4" s="16" t="inlineStr">
-        <is>
-          <t>Tekrar / Değerlendirme</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="17" t="inlineStr"/>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Yemek</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Günlük Tekrar</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Yatış Hazırlığı</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>Zaman Bloğu</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Pazartesi</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Salı</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>Çarşamba</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Perşembe</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>Cuma</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>Cumartesi</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>Pazar</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Blok 1
-(Ders Çalışması)</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>18:30–19:10
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Giriş / Dinlenme</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>17:30–17:40
+Eve Varış /
+Dinlenme</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>17:30–17:40
+Eve Varış /
+Dinlenme</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>17:30–17:40
+Eve Varış /
+Dinlenme</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>17:30–17:40
+Eve Varış /
+Dinlenme</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>17:30–17:40
+Eve Varış /
+Dinlenme</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>17:30–17:40
+Eve Varış /
+Dinlenme</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>17:30–17:40
+Eve Varış /
+Dinlenme</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Günlük Ödev</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>17:40–18:25
+Günlük Ödevler</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>17:40–18:25
+Günlük Ödevler</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>17:40–18:25
+Günlük Ödevler</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>17:40–18:25
+Günlük Ödevler</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>17:40–18:25
+Günlük Ödevler</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>17:40–18:25
+Günlük Ödevler</t>
+        </is>
+      </c>
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>17:40–18:25
+Günlük Ödevler</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>Mola</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>18:25–18:35
+Mola</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>18:25–18:35
+Mola</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>18:25–18:35
+Mola</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>18:25–18:35
+Mola</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="inlineStr">
+        <is>
+          <t>18:25–18:35
+Mola</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>18:25–18:35
+Mola</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="inlineStr">
+        <is>
+          <t>18:25–18:35
+Mola</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Ek Çalışma 1</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>18:35–19:20
 Matematik
 Konu Tekrarı</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>18:30–19:10
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>18:35–19:20
 Türkçe
 Konu Tekrarı</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>18:30–19:10
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>18:35–19:20
+Matematik
+Soru Çözümü</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>18:35–19:20
+Sosyal Bilgiler
+Soru Çözümü</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>18:35–19:20
+Fen Bilimleri
+Test Çözümü</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>18:35–19:20
+Matematik
+Yanlış Analizi</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>18:35–19:20
+Matematik
+Genel Tekrar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>Yemek</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>19:20–19:45
+Yemek</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>19:20–19:45
+Yemek</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>19:20–19:45
+Yemek</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>19:20–19:45
+Yemek</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>19:20–19:45
+Yemek</t>
+        </is>
+      </c>
+      <c r="G11" s="32" t="inlineStr">
+        <is>
+          <t>19:20–19:45
+Yemek</t>
+        </is>
+      </c>
+      <c r="H11" s="32" t="inlineStr">
+        <is>
+          <t>19:20–19:45
+Yemek</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Ek Çalışma 2</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>19:45–20:30
+Türkçe
+Soru Çözümü</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>19:45–20:30
+Matematik
+Soru Çözümü</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>19:45–20:30
+Fen Bilimleri
+Soru Çözümü</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>19:45–20:30
 Matematik
 Konu Tekrarı</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>18:30–19:10
+      <c r="F12" s="29" t="inlineStr">
+        <is>
+          <t>19:45–20:30
+Türkçe
+Soru Çözümü</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="inlineStr">
+        <is>
+          <t>19:45–20:30
 Sosyal Bilgiler
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
-        <is>
-          <t>18:30–19:10
+      <c r="H12" s="29" t="inlineStr">
+        <is>
+          <t>19:45–20:30
+Türkçe
+Genel Tekrar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Mola</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>20:30–20:40
+Mola</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>20:30–20:40
+Mola</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>20:30–20:40
+Mola</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>20:30–20:40
+Mola</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="inlineStr">
+        <is>
+          <t>20:30–20:40
+Mola</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>20:30–20:40
+Mola</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="inlineStr">
+        <is>
+          <t>20:30–20:40
+Mola</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Ek Çalışma 3</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>20:40–21:10
 Fen Bilimleri
 Konu Tekrarı</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>10:00–10:40
-Matematik
-Yanlış Analizi</t>
-        </is>
-      </c>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>10:00–10:40
-Matematik
-Genel Tekrar</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Mola</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>19:10–19:20
-Mola</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>19:10–19:20
-Mola</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>19:10–19:20
-Mola</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>19:10–19:20
-Mola</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>19:10–19:20
-Mola</t>
-        </is>
-      </c>
-      <c r="G7" s="23" t="inlineStr">
-        <is>
-          <t>10:40–10:50
-Mola</t>
-        </is>
-      </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>10:40–10:50
-Mola</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Blok 2
-(Ders Çalışması)</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>19:20–20:00
-Türkçe
-Soru Çözümü</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>19:20–20:00
-Matematik
-Soru Çözümü</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>19:20–20:00
-Fen Bilimleri
-Soru Çözümü</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>19:20–20:00
-Matematik
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>20:40–21:10
+Sosyal Bilgiler
 Konu Tekrarı</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>19:20–20:00
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>20:40–21:10
 Türkçe
 Test Çözümü</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>10:50–11:30
-Sosyal Bilgiler
-Soru Çözümü</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>10:50–11:30
-Türkçe
-Genel Tekrar</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Yemek /
-Uzun Mola</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>20:00–20:30
-Yemek / Uzun Mola</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>20:00–20:30
-Yemek / Uzun Mola</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>20:00–20:30
-Yemek / Uzun Mola</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>20:00–20:30
-Yemek / Uzun Mola</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t>20:00–20:30
-Yemek / Uzun Mola</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>11:30–15:00
-Serbest Zaman /
-Aile / Hobi</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>11:30–15:00
-Serbest Zaman /
-Aile</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Blok 3
-(Ders Çalışması)</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>20:30–21:10
-Fen Bilimleri
-Konu Tekrarı</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>20:30–21:10
-Sosyal Bilgiler
-Konu Tekrarı</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>20:30–21:10
-Türkçe
-Soru Çözümü</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>20:30–21:10
+      <c r="E14" s="29" t="inlineStr">
+        <is>
+          <t>20:40–21:10
 Türkçe
 Konu Tekrarı</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>20:30–21:10
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>20:40–21:10
 Matematik
 Test Çözümü</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
-        <is>
-          <t>15:00–15:40
+      <c r="G14" s="31" t="inlineStr">
+        <is>
+          <t>20:40–21:10
 Fen Bilimleri
 Test Çözümü</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>15:00–15:40
+      <c r="H14" s="31" t="inlineStr">
+        <is>
+          <t>20:40–21:10
 Fen Bil. &amp; Sosyal Bil.
 Genel Tekrar</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Mola</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>21:10–21:20
-Mola</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>21:10–21:20
-Mola</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>21:10–21:20
-Mola</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>21:10–21:20
-Mola</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>21:10–21:20
-Mola</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>15:40–15:50
-Mola</t>
-        </is>
-      </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>15:40–15:50
-Mola</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Kısa Tekrar /
-Değerlendirme</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>21:20–21:45
-Türkçe
-Kısa Tekrar (Kelime-Deyim)</t>
-        </is>
-      </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>21:20–21:45
-Serbest Okuma
-(Kitap)</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>21:20–21:45
-Matematik
-Yanlış Analizi</t>
-        </is>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>21:20–21:45
-Fen Bilimleri
-Kısa Tekrar</t>
-        </is>
-      </c>
-      <c r="F12" s="25" t="inlineStr">
-        <is>
-          <t>21:20–21:45
-Haftalık Genel
-Değerlendirme</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>15:50–16:30
-Türkçe
-Test Çözümü</t>
-        </is>
-      </c>
-      <c r="H12" s="25" t="inlineStr">
-        <is>
-          <t>15:50–16:30
-Haftalık Planlama /
-Değerlendirme</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Günlük Tekrar</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>21:10–21:55
+Günlük Tekrar
+(Bugünkü konuların özeti)</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>21:10–21:55
+Günlük Tekrar
+(Bugünkü konuların özeti)</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>21:10–21:55
+Günlük Tekrar
+(Bugünkü konuların özeti)</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>21:10–21:55
+Günlük Tekrar
+(Bugünkü konuların özeti)</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>21:10–21:55
+Günlük Tekrar
+(Bugünkü konuların özeti)</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="inlineStr">
+        <is>
+          <t>21:10–21:55
+Günlük Tekrar
+(Bugünkü konuların özeti)</t>
+        </is>
+      </c>
+      <c r="H15" s="33" t="inlineStr">
+        <is>
+          <t>21:10–21:55
+Günlük Tekrar
+(Bugünkü konuların özeti)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Yatış Hazırlığı</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>21:55–22:00
+Yatış Hazırlığı
+→ 22:00 Uyku</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>21:55–22:00
+Yatış Hazırlığı
+→ 22:00 Uyku</t>
+        </is>
+      </c>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>21:55–22:00
+Yatış Hazırlığı
+→ 22:00 Uyku</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="inlineStr">
+        <is>
+          <t>21:55–22:00
+Yatış Hazırlığı
+→ 22:00 Uyku</t>
+        </is>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>21:55–22:00
+Yatış Hazırlığı
+→ 22:00 Uyku</t>
+        </is>
+      </c>
+      <c r="G16" s="34" t="inlineStr">
+        <is>
+          <t>21:55–22:00
+Yatış Hazırlığı
+→ 22:00 Uyku</t>
+        </is>
+      </c>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
+          <t>21:55–22:00
+Yatış Hazırlığı
+→ 22:00 Uyku</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>Haftalık Ek Çalışma Dağılımı  —  Matematik: 7  |  Türkçe: 6  |  Fen Bilimleri: 5  |  Sosyal Bilgiler: 3   (Günlük Ödev + Günlük Tekrar: 1.5 saat, Ek Çalışma: 2 saat/gün)</t>
+        </is>
+      </c>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>NOTLAR</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="28" t="inlineStr"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="28" t="inlineStr"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="28" t="inlineStr"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="B20" s="38" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="38" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="38" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="39" t="inlineStr"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="39" t="inlineStr"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="39" t="inlineStr"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>“Düzenli çalışma, küçük adımların büyük sonuçlara dönüşmesidir.”</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-    </row>
-    <row r="20" ht="14" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="41" t="inlineStr">
         <is>
           <t>TED Okulları  |  Rehberlik Servisi  |  Hazırlayan: Merve Çelik</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
@@ -1364,128 +1654,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>Programı Nasıl Düzenlersiniz?</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="43" t="inlineStr">
+        <is>
+          <t>• Zaman Yapısı</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>Program 17:30 okul çıkışından 22:00 uyku saatine kadar sabit bir çerçeve üzerine kuruludur: Günlük Ödev + Günlük Tekrar toplam 1.5 saat, Ek Çalışma (3 blok) toplam 2 saat. İhtiyaca göre 2-3 saat aralığında uzatılabilir; bunun için Ek Çalışma bloklarının süresini ve Mola/Yemek sürelerini kısaltıp uzatarak yeniden dengeleyebilirsiniz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>• Ders Saatleri</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="33" t="inlineStr">
-        <is>
-          <t>Her hücredeki saat aralığını (örn. 18:30–19:10) doğrudan tıklayıp yazarak değiştirebilirsiniz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
-        <is>
-          <t>• Dersler ve Konular</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="33" t="inlineStr">
-        <is>
-          <t>"Haftalık Program" sayfasındaki her hücreye dersin adını ve yapılacak çalışma türünü (konu tekrarı, soru çözümü, test, yanlış analizi vb.) yazabilirsiniz.</t>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t>Her hücredeki saat aralığını (örn. 18:35–19:20) doğrudan tıklayıp yazarak değiştirebilirsiniz.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t>• Çalışma Süreleri</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
-        <is>
-          <t>Blok başlıkları (Blok 1, Blok 2, Blok 3) ve mola süreleri satırlardaki saatleri değiştirerek yeniden ayarlanabilir.</t>
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>• Ek Çalışma İçeriği</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>"Ek Çalışma 1/2/3" satırlarındaki hücrelere dersin adını ve çalışma türünü (konu tekrarı, soru çözümü, test, yanlış analizi vb.) yazabilirsiniz.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>• Öğrenciye Özel Görevler</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>"Kısa Tekrar / Değerlendirme" satırı ve NOTLAR bölümü, öğrenciye özel ek görev veya hatırlatma yazmak için kullanılabilir.</t>
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>• Uyku Saati</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>Program 22:00'de uyku hedefiyle tasarlanmıştır. Yatış saatini değiştirmek isterseniz son satırdaki "Yatış Hazırlığı" bloğunun saatini güncelleyip diğer blokları buna göre kaydırın.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>• Hafta İçi / Hafta Sonu</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>Cumartesi ve Pazar sütunlarındaki saatler, hafta içine göre daha esnek planlanmıştır; ihtiyaca göre yeniden düzenlenebilir.</t>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>Program şu an tüm hafta için aynı saat şablonunu kullanır (tutarlı uyku düzeni için). Hafta sonu daha esnek olmasını isterseniz Cumartesi/Pazar sütunlarındaki saatleri ayrı ayrı değiştirebilirsiniz.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>• Renk Kodları</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="33" t="inlineStr">
-        <is>
-          <t>Her ders türü farklı bir renkle gösterilir (bkz. sayfa üstündeki 'Renk Kodları' satırı). Yeni bir hücre eklerken ilgili dersin rengini Hücre &gt; Dolgu Rengi seçeneğinden uygulayabilirsiniz.</t>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>Her blok türü farklı bir renkle gösterilir (bkz. sayfa üstündeki 'Renk Kodları' satırları).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="43" t="inlineStr">
         <is>
           <t>• Logo Alanı</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="33" t="inlineStr">
-        <is>
-          <t>Sol üst köşedeki gri kutu TED okul logosu için ayrılmıştır. Logo görseli temin edildiğinde Ekle &gt; Resim ile bu alana yerleştirilebilir; kutu daha sonra silinebilir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="32" t="inlineStr">
-        <is>
-          <t>• Öğrenci / Hafta Bilgisi</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="33" t="inlineStr">
-        <is>
-          <t>Başlık altındaki 'Öğrenci Adı Soyadı' ve 'Hafta / Tarih Aralığı' alanları her hafta güncellenebilir.</t>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>Sol üst köşedeki gri kutu TED okul logosu için ayrılmıştır. Logo görseli temin edildiğinde Ekle &gt; Resim ile bu alana yerleştirilebilir.</t>
         </is>
       </c>
     </row>

--- a/7_Sinif_Haftalik_Ders_Calisma_Programi.xlsx
+++ b/7_Sinif_Haftalik_Ders_Calisma_Programi.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Nasıl Düzenlenir" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Haftalik Program'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Haftalik Program'!$A$1:$H$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -163,11 +163,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="004A148C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="001B5E20"/>
       <sz val="10"/>
     </font>
@@ -175,6 +170,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00827717"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="004A148C"/>
       <sz val="10"/>
     </font>
     <font>
@@ -435,13 +435,13 @@
     <xf numFmtId="0" fontId="23" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -837,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -875,7 +875,7 @@
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Rehber Öğretmen: Merve Çelik   |   Program: 17:30 Okul Çıkışı – 22:00 Uyku</t>
+          <t>Rehber Öğretmen: Merve Çelik   |   17:30 Okul Çıkışı → 1 sa Dinlenme → 22:00 Uyku</t>
         </is>
       </c>
       <c r="C2" s="6" t="n"/>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
+    <row r="7" ht="46" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Giriş / Dinlenme</t>
@@ -1018,55 +1018,55 @@
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>17:30–17:40
+          <t>17:30–18:30
 Eve Varış /
-Dinlenme</t>
+Dinlenme (1 sa)</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>17:30–17:40
+          <t>17:30–18:30
 Eve Varış /
-Dinlenme</t>
+Dinlenme (1 sa)</t>
         </is>
       </c>
       <c r="D7" s="25" t="inlineStr">
         <is>
-          <t>17:30–17:40
+          <t>17:30–18:30
 Eve Varış /
-Dinlenme</t>
+Dinlenme (1 sa)</t>
         </is>
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>17:30–17:40
+          <t>17:30–18:30
 Eve Varış /
-Dinlenme</t>
+Dinlenme (1 sa)</t>
         </is>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>17:30–17:40
+          <t>17:30–18:30
 Eve Varış /
-Dinlenme</t>
+Dinlenme (1 sa)</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>17:30–17:40
+          <t>17:30–18:30
 Eve Varış /
-Dinlenme</t>
+Dinlenme (1 sa)</t>
         </is>
       </c>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>17:30–17:40
+          <t>17:30–18:30
 Eve Varış /
-Dinlenme</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
+Dinlenme (1 sa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Günlük Ödev</t>
@@ -1074,48 +1074,48 @@
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>17:40–18:25
+          <t>18:30–19:15
 Günlük Ödevler</t>
         </is>
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>17:40–18:25
+          <t>18:30–19:15
 Günlük Ödevler</t>
         </is>
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>17:40–18:25
+          <t>18:30–19:15
 Günlük Ödevler</t>
         </is>
       </c>
       <c r="E8" s="26" t="inlineStr">
         <is>
-          <t>17:40–18:25
+          <t>18:30–19:15
 Günlük Ödevler</t>
         </is>
       </c>
       <c r="F8" s="26" t="inlineStr">
         <is>
-          <t>17:40–18:25
+          <t>18:30–19:15
 Günlük Ödevler</t>
         </is>
       </c>
       <c r="G8" s="26" t="inlineStr">
         <is>
-          <t>17:40–18:25
+          <t>18:30–19:15
 Günlük Ödevler</t>
         </is>
       </c>
       <c r="H8" s="26" t="inlineStr">
         <is>
-          <t>17:40–18:25
+          <t>18:30–19:15
 Günlük Ödevler</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Mola</t>
@@ -1123,44 +1123,44 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>18:25–18:35
-Mola</t>
+          <t>19:15–19:20
+Kısa Mola</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>18:25–18:35
-Mola</t>
+          <t>19:15–19:20
+Kısa Mola</t>
         </is>
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
-          <t>18:25–18:35
-Mola</t>
+          <t>19:15–19:20
+Kısa Mola</t>
         </is>
       </c>
       <c r="E9" s="27" t="inlineStr">
         <is>
-          <t>18:25–18:35
-Mola</t>
+          <t>19:15–19:20
+Kısa Mola</t>
         </is>
       </c>
       <c r="F9" s="27" t="inlineStr">
         <is>
-          <t>18:25–18:35
-Mola</t>
+          <t>19:15–19:20
+Kısa Mola</t>
         </is>
       </c>
       <c r="G9" s="27" t="inlineStr">
         <is>
-          <t>18:25–18:35
-Mola</t>
+          <t>19:15–19:20
+Kısa Mola</t>
         </is>
       </c>
       <c r="H9" s="27" t="inlineStr">
         <is>
-          <t>18:25–18:35
-Mola</t>
+          <t>19:15–19:20
+Kısa Mola</t>
         </is>
       </c>
     </row>
@@ -1172,313 +1172,257 @@
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
-          <t>18:35–19:20
+          <t>19:20–20:05
 Matematik
 Konu Tekrarı</t>
         </is>
       </c>
       <c r="C10" s="29" t="inlineStr">
         <is>
-          <t>18:35–19:20
+          <t>19:20–20:05
 Türkçe
 Konu Tekrarı</t>
         </is>
       </c>
       <c r="D10" s="28" t="inlineStr">
         <is>
-          <t>18:35–19:20
+          <t>19:20–20:05
 Matematik
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
-        <is>
-          <t>18:35–19:20
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>19:20–20:05
+Türkçe
+Konu Tekrarı</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>19:20–20:05
+Fen Bilimleri
+Test Çözümü</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>19:20–20:05
+Matematik
+Yanlış Analizi</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>19:20–20:05
+Matematik
+Genel Tekrar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>Yemek</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>20:05–20:20
+Yemek</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>20:05–20:20
+Yemek</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>20:05–20:20
+Yemek</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>20:05–20:20
+Yemek</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>20:05–20:20
+Yemek</t>
+        </is>
+      </c>
+      <c r="G11" s="31" t="inlineStr">
+        <is>
+          <t>20:05–20:20
+Yemek</t>
+        </is>
+      </c>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>20:05–20:20
+Yemek</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Ek Çalışma 2</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>20:20–21:05
+Türkçe
+Soru Çözümü</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>20:20–21:05
+Matematik
+Soru Çözümü</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>20:20–21:05
+Fen Bilimleri
+Soru Çözümü</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>20:20–21:05
 Sosyal Bilgiler
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="F10" s="31" t="inlineStr">
-        <is>
-          <t>18:35–19:20
-Fen Bilimleri
+      <c r="F12" s="29" t="inlineStr">
+        <is>
+          <t>20:20–21:05
+Türkçe
 Test Çözümü</t>
         </is>
       </c>
-      <c r="G10" s="28" t="inlineStr">
-        <is>
-          <t>18:35–19:20
-Matematik
-Yanlış Analizi</t>
-        </is>
-      </c>
-      <c r="H10" s="28" t="inlineStr">
-        <is>
-          <t>18:35–19:20
-Matematik
-Genel Tekrar</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>Yemek</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>19:20–19:45
-Yemek</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="inlineStr">
-        <is>
-          <t>19:20–19:45
-Yemek</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
-        <is>
-          <t>19:20–19:45
-Yemek</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>19:20–19:45
-Yemek</t>
-        </is>
-      </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>19:20–19:45
-Yemek</t>
-        </is>
-      </c>
-      <c r="G11" s="32" t="inlineStr">
-        <is>
-          <t>19:20–19:45
-Yemek</t>
-        </is>
-      </c>
-      <c r="H11" s="32" t="inlineStr">
-        <is>
-          <t>19:20–19:45
-Yemek</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>Ek Çalışma 2</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>19:45–20:30
-Türkçe
-Soru Çözümü</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t>19:45–20:30
-Matematik
-Soru Çözümü</t>
-        </is>
-      </c>
-      <c r="D12" s="31" t="inlineStr">
-        <is>
-          <t>19:45–20:30
-Fen Bilimleri
-Soru Çözümü</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="inlineStr">
-        <is>
-          <t>19:45–20:30
-Matematik
-Konu Tekrarı</t>
-        </is>
-      </c>
-      <c r="F12" s="29" t="inlineStr">
-        <is>
-          <t>19:45–20:30
-Türkçe
-Soru Çözümü</t>
-        </is>
-      </c>
-      <c r="G12" s="30" t="inlineStr">
-        <is>
-          <t>19:45–20:30
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t>20:20–21:05
 Sosyal Bilgiler
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="H12" s="29" t="inlineStr">
-        <is>
-          <t>19:45–20:30
-Türkçe
-Genel Tekrar</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>Mola</t>
-        </is>
-      </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>20:30–20:40
-Mola</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>20:30–20:40
-Mola</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>20:30–20:40
-Mola</t>
-        </is>
-      </c>
-      <c r="E13" s="27" t="inlineStr">
-        <is>
-          <t>20:30–20:40
-Mola</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="inlineStr">
-        <is>
-          <t>20:30–20:40
-Mola</t>
-        </is>
-      </c>
-      <c r="G13" s="27" t="inlineStr">
-        <is>
-          <t>20:30–20:40
-Mola</t>
-        </is>
-      </c>
-      <c r="H13" s="27" t="inlineStr">
-        <is>
-          <t>20:30–20:40
-Mola</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>Ek Çalışma 3</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>20:40–21:10
-Fen Bilimleri
-Konu Tekrarı</t>
-        </is>
-      </c>
-      <c r="C14" s="30" t="inlineStr">
-        <is>
-          <t>20:40–21:10
-Sosyal Bilgiler
-Konu Tekrarı</t>
-        </is>
-      </c>
-      <c r="D14" s="29" t="inlineStr">
-        <is>
-          <t>20:40–21:10
-Türkçe
-Test Çözümü</t>
-        </is>
-      </c>
-      <c r="E14" s="29" t="inlineStr">
-        <is>
-          <t>20:40–21:10
-Türkçe
-Konu Tekrarı</t>
-        </is>
-      </c>
-      <c r="F14" s="28" t="inlineStr">
-        <is>
-          <t>20:40–21:10
-Matematik
-Test Çözümü</t>
-        </is>
-      </c>
-      <c r="G14" s="31" t="inlineStr">
-        <is>
-          <t>20:40–21:10
-Fen Bilimleri
-Test Çözümü</t>
-        </is>
-      </c>
-      <c r="H14" s="31" t="inlineStr">
-        <is>
-          <t>20:40–21:10
+      <c r="H12" s="30" t="inlineStr">
+        <is>
+          <t>20:20–21:05
 Fen Bil. &amp; Sosyal Bil.
 Genel Tekrar</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Mola</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>21:05–21:10
+Kısa Mola</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>21:05–21:10
+Kısa Mola</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>21:05–21:10
+Kısa Mola</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>21:05–21:10
+Kısa Mola</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="inlineStr">
+        <is>
+          <t>21:05–21:10
+Kısa Mola</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>21:05–21:10
+Kısa Mola</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="inlineStr">
+        <is>
+          <t>21:05–21:10
+Kısa Mola</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Günlük Tekrar</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>21:10–21:55
 Günlük Tekrar
 (Bugünkü konuların özeti)</t>
         </is>
       </c>
-      <c r="C15" s="33" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>21:10–21:55
 Günlük Tekrar
 (Bugünkü konuların özeti)</t>
         </is>
       </c>
-      <c r="D15" s="33" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>21:10–21:55
 Günlük Tekrar
 (Bugünkü konuların özeti)</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>21:10–21:55
 Günlük Tekrar
 (Bugünkü konuların özeti)</t>
         </is>
       </c>
-      <c r="F15" s="33" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>21:10–21:55
 Günlük Tekrar
 (Bugünkü konuların özeti)</t>
         </is>
       </c>
-      <c r="G15" s="33" t="inlineStr">
+      <c r="G14" s="33" t="inlineStr">
         <is>
           <t>21:10–21:55
 Günlük Tekrar
 (Bugünkü konuların özeti)</t>
         </is>
       </c>
-      <c r="H15" s="33" t="inlineStr">
+      <c r="H14" s="33" t="inlineStr">
         <is>
           <t>21:10–21:55
 Günlük Tekrar
@@ -1486,55 +1430,55 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Yatış Hazırlığı</t>
         </is>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>21:55–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>21:55–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
+      <c r="D15" s="34" t="inlineStr">
         <is>
           <t>21:55–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-      <c r="E16" s="34" t="inlineStr">
+      <c r="E15" s="34" t="inlineStr">
         <is>
           <t>21:55–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-      <c r="F16" s="34" t="inlineStr">
+      <c r="F15" s="34" t="inlineStr">
         <is>
           <t>21:55–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-      <c r="G16" s="34" t="inlineStr">
+      <c r="G15" s="34" t="inlineStr">
         <is>
           <t>21:55–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-      <c r="H16" s="34" t="inlineStr">
+      <c r="H15" s="34" t="inlineStr">
         <is>
           <t>21:55–22:00
 Yatış Hazırlığı
@@ -1542,33 +1486,43 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>Haftalık Ek Çalışma Dağılımı  —  Matematik: 7  |  Türkçe: 6  |  Fen Bilimleri: 5  |  Sosyal Bilgiler: 3   (Günlük Ödev + Günlük Tekrar: 1.5 saat, Ek Çalışma: 2 saat/gün)</t>
-        </is>
-      </c>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
-      <c r="H18" s="36" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>Haftalık Ek Çalışma Dağılımı  —  Matematik: 5  |  Türkçe: 4  |  Fen Bilimleri: 3  |  Sosyal Bilgiler: 2   (Dinlenme: 1 saat, Günlük Ödev + Günlük Tekrar: 1.5 saat, Ek Çalışma: 1.5 saat/gün, Uyku: 22:00)</t>
+        </is>
+      </c>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>NOTLAR</t>
         </is>
       </c>
-      <c r="B20" s="38" t="n"/>
-      <c r="C20" s="38" t="n"/>
-      <c r="D20" s="38" t="n"/>
-      <c r="E20" s="38" t="n"/>
-      <c r="F20" s="38" t="n"/>
-      <c r="G20" s="38" t="n"/>
-      <c r="H20" s="38" t="n"/>
+      <c r="B19" s="38" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="38" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="39" t="inlineStr"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="39" t="inlineStr"/>
@@ -1590,58 +1544,48 @@
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="39" t="inlineStr"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="40" t="inlineStr">
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>“Düzenli çalışma, küçük adımların büyük sonuçlara dönüşmesidir.”</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-    </row>
-    <row r="26" ht="14" customHeight="1">
-      <c r="A26" s="41" t="inlineStr">
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="41" t="inlineStr">
         <is>
           <t>TED Okulları  |  Rehberlik Servisi  |  Hazırlayan: Merve Çelik</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
+      <c r="H25" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A26:H26"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
@@ -1654,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1677,7 +1621,7 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="44" t="inlineStr">
         <is>
-          <t>Program 17:30 okul çıkışından 22:00 uyku saatine kadar sabit bir çerçeve üzerine kuruludur: Günlük Ödev + Günlük Tekrar toplam 1.5 saat, Ek Çalışma (3 blok) toplam 2 saat. İhtiyaca göre 2-3 saat aralığında uzatılabilir; bunun için Ek Çalışma bloklarının süresini ve Mola/Yemek sürelerini kısaltıp uzatarak yeniden dengeleyebilirsiniz.</t>
+          <t>17:30 okul çıkışından 22:00 uyku saatine kadar 270 dakikalık sabit bir pencere kullanılır: 1 saat dinlenme + 1.5 saat günlük ödev/tekrar + 1.5 saat ek çalışma + kısa molalar + yemek + yatış hazırlığı tam olarak bu süreye oturacak şekilde ayarlanmıştır.</t>
         </is>
       </c>
     </row>
@@ -1691,75 +1635,89 @@
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>Her hücredeki saat aralığını (örn. 18:35–19:20) doğrudan tıklayıp yazarak değiştirebilirsiniz.</t>
+          <t>Her hücredeki saat aralığını (örn. 19:20–20:05) doğrudan tıklayıp yazarak değiştirebilirsiniz.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="43" t="inlineStr">
         <is>
-          <t>• Ek Çalışma İçeriği</t>
+          <t>• Süreleri Yeniden Dengeleme</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>"Ek Çalışma 1/2/3" satırlarındaki hücrelere dersin adını ve çalışma türünü (konu tekrarı, soru çözümü, test, yanlış analizi vb.) yazabilirsiniz.</t>
+          <t>Bir bloğun süresini uzatmak isterseniz (örn. Ek Çalışmayı 1.5 saatten 2 saate çıkarmak), başka bir bloktan (mola, yemek veya dinlenme) o kadar dakika kısarak toplamı 270 dakikada sabit tutmanız gerekir; aksi halde 22:00 uyku hedefi kayar.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="43" t="inlineStr">
         <is>
-          <t>• Uyku Saati</t>
+          <t>• Ek Çalışma İçeriği</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>Program 22:00'de uyku hedefiyle tasarlanmıştır. Yatış saatini değiştirmek isterseniz son satırdaki "Yatış Hazırlığı" bloğunun saatini güncelleyip diğer blokları buna göre kaydırın.</t>
+          <t>"Ek Çalışma 1/2" satırlarındaki hücrelere dersin adını ve çalışma türünü (konu tekrarı, soru çözümü, test, yanlış analizi vb.) yazabilirsiniz.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>• Hafta İçi / Hafta Sonu</t>
+          <t>• Uyku Saati</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>Program şu an tüm hafta için aynı saat şablonunu kullanır (tutarlı uyku düzeni için). Hafta sonu daha esnek olmasını isterseniz Cumartesi/Pazar sütunlarındaki saatleri ayrı ayrı değiştirebilirsiniz.</t>
+          <t>Program 22:00'de uyku hedefiyle tasarlanmıştır. Yatış saatini değiştirmek isterseniz son satırdaki "Yatış Hazırlığı" bloğunun saatini güncelleyip diğer blokları buna göre kaydırın.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="43" t="inlineStr">
         <is>
-          <t>• Renk Kodları</t>
+          <t>• Hafta İçi / Hafta Sonu</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>Her blok türü farklı bir renkle gösterilir (bkz. sayfa üstündeki 'Renk Kodları' satırları).</t>
+          <t>Program şu an tüm hafta için aynı saat şablonunu kullanır (tutarlı uyku düzeni için). Hafta sonu daha esnek olmasını isterseniz Cumartesi/Pazar sütunlarındaki saatleri ayrı ayrı değiştirebilirsiniz.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="43" t="inlineStr">
         <is>
-          <t>• Logo Alanı</t>
+          <t>• Renk Kodları</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>Her blok türü farklı bir renkle gösterilir (bkz. sayfa üstündeki 'Renk Kodları' satırları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>• Logo Alanı</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="44" t="inlineStr">
         <is>
           <t>Sol üst köşedeki gri kutu TED okul logosu için ayrılmıştır. Logo görseli temin edildiğinde Ekle &gt; Resim ile bu alana yerleştirilebilir.</t>
         </is>

--- a/7_Sinif_Haftalik_Ders_Calisma_Programi.xlsx
+++ b/7_Sinif_Haftalik_Ders_Calisma_Programi.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Nasıl Düzenlenir" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Haftalik Program'!$A$1:$H$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Haftalik Program'!$A$1:$H$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="34">
+  <fonts count="49">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,7 +45,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3B57"/>
-      <sz val="12"/>
+      <sz val="11.5"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -119,6 +119,18 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="006D1F35"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005C5041"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
@@ -126,7 +138,13 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11.5"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -138,6 +156,93 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="0037474F"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A237E"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00455A64"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00BF360C"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000D47A1"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001B5E20"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00827717"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="004A148C"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0000695C"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006D1F35"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00311B92"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0037474F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00BF360C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00455A64"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="004A148C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001B5E20"/>
       <sz val="10"/>
     </font>
     <font>
@@ -148,38 +253,19 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00455A64"/>
+      <color rgb="005C5041"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00BF360C"/>
+      <b val="1"/>
+      <color rgb="0000695C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000D47A1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001B5E20"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00827717"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="004A148C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0000695C"/>
+      <b val="1"/>
+      <color rgb="006D1F35"/>
       <sz val="10"/>
     </font>
     <font>
@@ -220,7 +306,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -319,6 +405,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F6E2E7"/>
+        <bgColor rgb="00F6E2E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEAE3"/>
+        <bgColor rgb="00EFEAE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003C5E82"/>
+        <bgColor rgb="003C5E82"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F3B57"/>
         <bgColor rgb="001F3B57"/>
       </patternFill>
@@ -356,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -410,65 +514,122 @@
     <xf numFmtId="0" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -837,17 +998,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="15.5" customWidth="1" min="2" max="2"/>
+    <col width="15.5" customWidth="1" min="3" max="3"/>
+    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="15.5" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="6" max="6"/>
+    <col width="15.5" customWidth="1" min="7" max="7"/>
+    <col width="15.5" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -875,7 +1036,7 @@
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Rehber Öğretmen: Merve Çelik   |   17:30 Okul Çıkışı → 1 sa Dinlenme → 22:00 Uyku</t>
+          <t>Rehber Öğretmen: Merve Çelik   |   Hafta İçi: 17:30 Çıkış → 22:00 Uyku   |   Hafta Sonu: Gün Boyu Program</t>
         </is>
       </c>
       <c r="C2" s="6" t="n"/>
@@ -963,632 +1124,900 @@
           <t>Yatış Hazırlığı</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr"/>
-      <c r="F5" s="21" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr"/>
-      <c r="H5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>Kitap Okuma</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>Serbest Zaman</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr"/>
+      <c r="H5" s="23" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>HAFTA İÇİ PROGRAMI  (Pazartesi – Cuma)   ·   17:30 Okul Çıkışı → 22:00 Uyku</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n"/>
+      <c r="C6" s="25" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="25" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Zaman Bloğu</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Pazartesi</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Salı</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Çarşamba</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>Perşembe</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>Cuma</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>Cumartesi</t>
-        </is>
-      </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>Pazar</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr"/>
+      <c r="H7" s="28" t="inlineStr"/>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Giriş / Dinlenme</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>17:30–18:30
 Eve Varış /
 Dinlenme (1 sa)</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>17:30–18:30
 Eve Varış /
 Dinlenme (1 sa)</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>17:30–18:30
 Eve Varış /
 Dinlenme (1 sa)</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>17:30–18:30
 Eve Varış /
 Dinlenme (1 sa)</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>17:30–18:30
 Eve Varış /
 Dinlenme (1 sa)</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
-        <is>
-          <t>17:30–18:30
-Eve Varış /
-Dinlenme (1 sa)</t>
-        </is>
-      </c>
-      <c r="H7" s="25" t="inlineStr">
-        <is>
-          <t>17:30–18:30
-Eve Varış /
-Dinlenme (1 sa)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr"/>
+      <c r="H8" s="28" t="inlineStr"/>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Günlük Ödev</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>18:30–19:15
 Günlük Ödevler</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>18:30–19:15
 Günlük Ödevler</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>18:30–19:15
 Günlük Ödevler</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>18:30–19:15
 Günlük Ödevler</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F9" s="31" t="inlineStr">
         <is>
           <t>18:30–19:15
 Günlük Ödevler</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
-        <is>
-          <t>18:30–19:15
-Günlük Ödevler</t>
-        </is>
-      </c>
-      <c r="H8" s="26" t="inlineStr">
-        <is>
-          <t>18:30–19:15
-Günlük Ödevler</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr"/>
+      <c r="H9" s="28" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Mola</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>19:15–19:20
-Kısa Mola</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
+Mola</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>19:15–19:20
-Kısa Mola</t>
-        </is>
-      </c>
-      <c r="D9" s="27" t="inlineStr">
+Mola</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>19:15–19:20
-Kısa Mola</t>
-        </is>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
+Mola</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>19:15–19:20
-Kısa Mola</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="inlineStr">
+Mola</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>19:15–19:20
-Kısa Mola</t>
-        </is>
-      </c>
-      <c r="G9" s="27" t="inlineStr">
-        <is>
-          <t>19:15–19:20
-Kısa Mola</t>
-        </is>
-      </c>
-      <c r="H9" s="27" t="inlineStr">
-        <is>
-          <t>19:15–19:20
-Kısa Mola</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+Mola</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr"/>
+      <c r="H10" s="28" t="inlineStr"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Ek Çalışma 1</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
-        <is>
-          <t>19:20–20:05
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>19:20–20:00
 Matematik
 Konu Tekrarı</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
-        <is>
-          <t>19:20–20:05
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>19:20–20:00
 Türkçe
 Konu Tekrarı</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
-        <is>
-          <t>19:20–20:05
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>19:20–20:00
 Matematik
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="E10" s="29" t="inlineStr">
-        <is>
-          <t>19:20–20:05
+      <c r="E11" s="34" t="inlineStr">
+        <is>
+          <t>19:20–20:00
 Türkçe
 Konu Tekrarı</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
-        <is>
-          <t>19:20–20:05
+      <c r="F11" s="35" t="inlineStr">
+        <is>
+          <t>19:20–20:00
 Fen Bilimleri
 Test Çözümü</t>
         </is>
       </c>
-      <c r="G10" s="28" t="inlineStr">
-        <is>
-          <t>19:20–20:05
-Matematik
-Yanlış Analizi</t>
-        </is>
-      </c>
-      <c r="H10" s="28" t="inlineStr">
-        <is>
-          <t>19:20–20:05
-Matematik
-Genel Tekrar</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr"/>
+      <c r="H11" s="28" t="inlineStr"/>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Yemek</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>20:05–20:20
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>20:00–20:15
 Yemek</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t>20:05–20:20
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>20:00–20:15
 Yemek</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
-        <is>
-          <t>20:05–20:20
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>20:00–20:15
 Yemek</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr">
-        <is>
-          <t>20:05–20:20
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>20:00–20:15
 Yemek</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr">
-        <is>
-          <t>20:05–20:20
+      <c r="F12" s="36" t="inlineStr">
+        <is>
+          <t>20:00–20:15
 Yemek</t>
         </is>
       </c>
-      <c r="G11" s="31" t="inlineStr">
-        <is>
-          <t>20:05–20:20
-Yemek</t>
-        </is>
-      </c>
-      <c r="H11" s="31" t="inlineStr">
-        <is>
-          <t>20:05–20:20
-Yemek</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr"/>
+      <c r="H12" s="28" t="inlineStr"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Ek Çalışma 2</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>20:20–21:05
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>20:15–20:50
 Türkçe
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t>20:20–21:05
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>20:15–20:50
 Matematik
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="D12" s="30" t="inlineStr">
-        <is>
-          <t>20:20–21:05
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>20:15–20:50
 Fen Bilimleri
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>20:20–21:05
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>20:15–20:50
 Sosyal Bilgiler
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="F12" s="29" t="inlineStr">
-        <is>
-          <t>20:20–21:05
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>20:15–20:50
 Türkçe
 Test Çözümü</t>
         </is>
       </c>
-      <c r="G12" s="32" t="inlineStr">
-        <is>
-          <t>20:20–21:05
-Sosyal Bilgiler
-Soru Çözümü</t>
-        </is>
-      </c>
-      <c r="H12" s="30" t="inlineStr">
-        <is>
-          <t>20:20–21:05
-Fen Bil. &amp; Sosyal Bil.
-Genel Tekrar</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr"/>
+      <c r="H13" s="28" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>Mola</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>21:05–21:10
-Kısa Mola</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>21:05–21:10
-Kısa Mola</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>21:05–21:10
-Kısa Mola</t>
-        </is>
-      </c>
-      <c r="E13" s="27" t="inlineStr">
-        <is>
-          <t>21:05–21:10
-Kısa Mola</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="inlineStr">
-        <is>
-          <t>21:05–21:10
-Kısa Mola</t>
-        </is>
-      </c>
-      <c r="G13" s="27" t="inlineStr">
-        <is>
-          <t>21:05–21:10
-Kısa Mola</t>
-        </is>
-      </c>
-      <c r="H13" s="27" t="inlineStr">
-        <is>
-          <t>21:05–21:10
-Kısa Mola</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>20:50–20:55
+Mola</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>20:50–20:55
+Mola</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>20:50–20:55
+Mola</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>20:50–20:55
+Mola</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>20:50–20:55
+Mola</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="inlineStr"/>
+      <c r="H14" s="28" t="inlineStr"/>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>Günlük Tekrar</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr">
-        <is>
-          <t>21:10–21:55
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>20:55–21:40
 Günlük Tekrar
 (Bugünkü konuların özeti)</t>
         </is>
       </c>
-      <c r="C14" s="33" t="inlineStr">
-        <is>
-          <t>21:10–21:55
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>20:55–21:40
 Günlük Tekrar
 (Bugünkü konuların özeti)</t>
         </is>
       </c>
-      <c r="D14" s="33" t="inlineStr">
-        <is>
-          <t>21:10–21:55
+      <c r="D15" s="38" t="inlineStr">
+        <is>
+          <t>20:55–21:40
 Günlük Tekrar
 (Bugünkü konuların özeti)</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
-        <is>
-          <t>21:10–21:55
+      <c r="E15" s="38" t="inlineStr">
+        <is>
+          <t>20:55–21:40
 Günlük Tekrar
 (Bugünkü konuların özeti)</t>
         </is>
       </c>
-      <c r="F14" s="33" t="inlineStr">
-        <is>
-          <t>21:10–21:55
+      <c r="F15" s="38" t="inlineStr">
+        <is>
+          <t>20:55–21:40
 Günlük Tekrar
 (Bugünkü konuların özeti)</t>
         </is>
       </c>
-      <c r="G14" s="33" t="inlineStr">
-        <is>
-          <t>21:10–21:55
-Günlük Tekrar
-(Bugünkü konuların özeti)</t>
-        </is>
-      </c>
-      <c r="H14" s="33" t="inlineStr">
-        <is>
-          <t>21:10–21:55
-Günlük Tekrar
-(Bugünkü konuların özeti)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr"/>
+      <c r="H15" s="28" t="inlineStr"/>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Kitap Okuma</t>
+        </is>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>21:40–21:55
+Kitap Okuma</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t>21:40–21:55
+Kitap Okuma</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>21:40–21:55
+Kitap Okuma</t>
+        </is>
+      </c>
+      <c r="E16" s="39" t="inlineStr">
+        <is>
+          <t>21:40–21:55
+Kitap Okuma</t>
+        </is>
+      </c>
+      <c r="F16" s="39" t="inlineStr">
+        <is>
+          <t>21:40–21:55
+Kitap Okuma</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="inlineStr"/>
+      <c r="H16" s="28" t="inlineStr"/>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Yatış Hazırlığı</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>21:55–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>21:55–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-      <c r="D15" s="34" t="inlineStr">
+      <c r="D17" s="40" t="inlineStr">
         <is>
           <t>21:55–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-      <c r="E15" s="34" t="inlineStr">
+      <c r="E17" s="40" t="inlineStr">
         <is>
           <t>21:55–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-      <c r="F15" s="34" t="inlineStr">
+      <c r="F17" s="40" t="inlineStr">
         <is>
           <t>21:55–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-      <c r="G15" s="34" t="inlineStr">
-        <is>
-          <t>21:55–22:00
+      <c r="G17" s="28" t="inlineStr"/>
+      <c r="H17" s="28" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>HAFTA SONU PROGRAMI  (Cumartesi – Pazar)   ·   Gün Boyu  ·  09:00 Uyanış → 22:00 Uyku</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="25" t="n"/>
+      <c r="H19" s="25" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Zaman Bloğu</t>
+        </is>
+      </c>
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>Cumartesi</t>
+        </is>
+      </c>
+      <c r="C20" s="42" t="n"/>
+      <c r="D20" s="42" t="n"/>
+      <c r="E20" s="41" t="inlineStr">
+        <is>
+          <t>Pazar</t>
+        </is>
+      </c>
+      <c r="F20" s="42" t="n"/>
+      <c r="G20" s="42" t="n"/>
+      <c r="H20" s="28" t="inlineStr"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Uyanış / Kahvaltı</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>09:00–09:30
+Uyanış / Kahvaltı</t>
+        </is>
+      </c>
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="43" t="inlineStr">
+        <is>
+          <t>09:00–09:30
+Uyanış / Kahvaltı</t>
+        </is>
+      </c>
+      <c r="F21" s="44" t="n"/>
+      <c r="G21" s="44" t="n"/>
+      <c r="H21" s="28" t="inlineStr"/>
+    </row>
+    <row r="22" ht="50" customHeight="1">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>Ek Çalışma 1</t>
+        </is>
+      </c>
+      <c r="B22" s="45" t="inlineStr">
+        <is>
+          <t>09:30–10:15
+Matematik
+Yanlış Analizi</t>
+        </is>
+      </c>
+      <c r="C22" s="46" t="n"/>
+      <c r="D22" s="46" t="n"/>
+      <c r="E22" s="45" t="inlineStr">
+        <is>
+          <t>09:30–10:15
+Matematik
+Genel Tekrar</t>
+        </is>
+      </c>
+      <c r="F22" s="46" t="n"/>
+      <c r="G22" s="46" t="n"/>
+      <c r="H22" s="28" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Mola</t>
+        </is>
+      </c>
+      <c r="B23" s="47" t="inlineStr">
+        <is>
+          <t>10:15–10:25
+Mola</t>
+        </is>
+      </c>
+      <c r="C23" s="48" t="n"/>
+      <c r="D23" s="48" t="n"/>
+      <c r="E23" s="47" t="inlineStr">
+        <is>
+          <t>10:15–10:25
+Mola</t>
+        </is>
+      </c>
+      <c r="F23" s="48" t="n"/>
+      <c r="G23" s="48" t="n"/>
+      <c r="H23" s="28" t="inlineStr"/>
+    </row>
+    <row r="24" ht="50" customHeight="1">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Ek Çalışma 2</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="inlineStr">
+        <is>
+          <t>10:25–11:10
+Sosyal Bilgiler
+Soru Çözümü</t>
+        </is>
+      </c>
+      <c r="C24" s="50" t="n"/>
+      <c r="D24" s="50" t="n"/>
+      <c r="E24" s="51" t="inlineStr">
+        <is>
+          <t>10:25–11:10
+Fen Bil. &amp; Sosyal Bil.
+Genel Tekrar</t>
+        </is>
+      </c>
+      <c r="F24" s="52" t="n"/>
+      <c r="G24" s="52" t="n"/>
+      <c r="H24" s="28" t="inlineStr"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>Ödev / Proje</t>
+        </is>
+      </c>
+      <c r="B25" s="53" t="inlineStr">
+        <is>
+          <t>11:10–12:00
+Günlük Ödev /
+Proje Çalışması</t>
+        </is>
+      </c>
+      <c r="C25" s="54" t="n"/>
+      <c r="D25" s="54" t="n"/>
+      <c r="E25" s="53" t="inlineStr">
+        <is>
+          <t>11:10–12:00
+Haftaya Hazırlık
+(Çanta, Kıyafet vb.)</t>
+        </is>
+      </c>
+      <c r="F25" s="54" t="n"/>
+      <c r="G25" s="54" t="n"/>
+      <c r="H25" s="28" t="inlineStr"/>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Öğle + Serbest Zaman</t>
+        </is>
+      </c>
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t>12:00–16:00
+Öğle Yemeği +
+Serbest Zaman
+(Aile / Hobi / Spor)</t>
+        </is>
+      </c>
+      <c r="C26" s="56" t="n"/>
+      <c r="D26" s="56" t="n"/>
+      <c r="E26" s="55" t="inlineStr">
+        <is>
+          <t>12:00–16:00
+Öğle Yemeği +
+Serbest Zaman
+(Aile / Hobi / Spor)</t>
+        </is>
+      </c>
+      <c r="F26" s="56" t="n"/>
+      <c r="G26" s="56" t="n"/>
+      <c r="H26" s="28" t="inlineStr"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>Günlük Tekrar</t>
+        </is>
+      </c>
+      <c r="B27" s="57" t="inlineStr">
+        <is>
+          <t>16:00–16:45
+Günlük Tekrar</t>
+        </is>
+      </c>
+      <c r="C27" s="58" t="n"/>
+      <c r="D27" s="58" t="n"/>
+      <c r="E27" s="57" t="inlineStr">
+        <is>
+          <t>16:00–16:45
+Haftalık Genel
+Değerlendirme</t>
+        </is>
+      </c>
+      <c r="F27" s="58" t="n"/>
+      <c r="G27" s="58" t="n"/>
+      <c r="H27" s="28" t="inlineStr"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>Kitap Okuma</t>
+        </is>
+      </c>
+      <c r="B28" s="59" t="inlineStr">
+        <is>
+          <t>16:45–17:15
+Kitap Okuma</t>
+        </is>
+      </c>
+      <c r="C28" s="60" t="n"/>
+      <c r="D28" s="60" t="n"/>
+      <c r="E28" s="59" t="inlineStr">
+        <is>
+          <t>16:45–17:15
+Kitap Okuma</t>
+        </is>
+      </c>
+      <c r="F28" s="60" t="n"/>
+      <c r="G28" s="60" t="n"/>
+      <c r="H28" s="28" t="inlineStr"/>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>Akşam + Serbest Zaman</t>
+        </is>
+      </c>
+      <c r="B29" s="55" t="inlineStr">
+        <is>
+          <t>17:15–21:30
+Akşam Yemeği +
+Serbest Zaman / Aile</t>
+        </is>
+      </c>
+      <c r="C29" s="56" t="n"/>
+      <c r="D29" s="56" t="n"/>
+      <c r="E29" s="55" t="inlineStr">
+        <is>
+          <t>17:15–21:30
+Akşam Yemeği +
+Serbest Zaman / Aile</t>
+        </is>
+      </c>
+      <c r="F29" s="56" t="n"/>
+      <c r="G29" s="56" t="n"/>
+      <c r="H29" s="28" t="inlineStr"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>Yatış Hazırlığı</t>
+        </is>
+      </c>
+      <c r="B30" s="61" t="inlineStr">
+        <is>
+          <t>21:30–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-      <c r="H15" s="34" t="inlineStr">
-        <is>
-          <t>21:55–22:00
+      <c r="C30" s="62" t="n"/>
+      <c r="D30" s="62" t="n"/>
+      <c r="E30" s="61" t="inlineStr">
+        <is>
+          <t>21:30–22:00
 Yatış Hazırlığı
 → 22:00 Uyku</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>Haftalık Ek Çalışma Dağılımı  —  Matematik: 5  |  Türkçe: 4  |  Fen Bilimleri: 3  |  Sosyal Bilgiler: 2   (Dinlenme: 1 saat, Günlük Ödev + Günlük Tekrar: 1.5 saat, Ek Çalışma: 1.5 saat/gün, Uyku: 22:00)</t>
-        </is>
-      </c>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
-      <c r="H17" s="36" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="F30" s="62" t="n"/>
+      <c r="G30" s="62" t="n"/>
+      <c r="H30" s="28" t="inlineStr"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="63" t="inlineStr">
+        <is>
+          <t>Haftalık Ek Çalışma Dağılımı  —  Matematik: 5  |  Türkçe: 4  |  Fen Bilimleri: 3  |  Sosyal Bilgiler: 2   ·   Kitap Okuma: 7 gün / 7 gün   ·   Uyku: Her gün 22:00</t>
+        </is>
+      </c>
+      <c r="B32" s="64" t="n"/>
+      <c r="C32" s="64" t="n"/>
+      <c r="D32" s="64" t="n"/>
+      <c r="E32" s="64" t="n"/>
+      <c r="F32" s="64" t="n"/>
+      <c r="G32" s="64" t="n"/>
+      <c r="H32" s="64" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="65" t="inlineStr">
         <is>
           <t>NOTLAR</t>
         </is>
       </c>
-      <c r="B19" s="38" t="n"/>
-      <c r="C19" s="38" t="n"/>
-      <c r="D19" s="38" t="n"/>
-      <c r="E19" s="38" t="n"/>
-      <c r="F19" s="38" t="n"/>
-      <c r="G19" s="38" t="n"/>
-      <c r="H19" s="38" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="39" t="inlineStr"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="39" t="inlineStr"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="39" t="inlineStr"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="40" t="inlineStr">
+      <c r="B34" s="42" t="n"/>
+      <c r="C34" s="42" t="n"/>
+      <c r="D34" s="42" t="n"/>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="42" t="n"/>
+      <c r="G34" s="42" t="n"/>
+      <c r="H34" s="42" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="66" t="inlineStr"/>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="8" t="n"/>
+      <c r="H35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="66" t="inlineStr"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="66" t="inlineStr"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="67" t="inlineStr">
         <is>
           <t>“Düzenli çalışma, küçük adımların büyük sonuçlara dönüşmesidir.”</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-    </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="41" t="inlineStr">
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="68" t="inlineStr">
         <is>
           <t>TED Okulları  |  Rehberlik Servisi  |  Hazırlayan: Merve Çelik</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="36">
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:A3"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="E24:G24"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1605,119 +2034,119 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>Programı Nasıl Düzenlersiniz?</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="43" t="inlineStr">
-        <is>
-          <t>• Zaman Yapısı</t>
+      <c r="A3" s="70" t="inlineStr">
+        <is>
+          <t>• İki Ayrı Tablo</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="44" t="inlineStr">
-        <is>
-          <t>17:30 okul çıkışından 22:00 uyku saatine kadar 270 dakikalık sabit bir pencere kullanılır: 1 saat dinlenme + 1.5 saat günlük ödev/tekrar + 1.5 saat ek çalışma + kısa molalar + yemek + yatış hazırlığı tam olarak bu süreye oturacak şekilde ayarlanmıştır.</t>
+      <c r="A4" s="71" t="inlineStr">
+        <is>
+          <t>Hafta içi (Pazartesi–Cuma) 17:30–22:00 arası okul sonrası akışını, hafta sonu (Cumartesi–Pazar) ise 09:00–22:00 arası gün boyu akışını gösterir. İki tablo farklı saat yapıları kullandığı için ayrı gösterilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
+        <is>
+          <t>• Kitap Okuma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="71" t="inlineStr">
+        <is>
+          <t>Her gün (hafta içi 15 dk, hafta sonu 30 dk) sabit bir 'Kitap Okuma' bloğu bulunur. Süresini veya saatini değiştirmek isterseniz ilgili hücreyi ve komşu bloğun süresini birlikte güncelleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="70" t="inlineStr">
         <is>
           <t>• Ders Saatleri</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
-        <is>
-          <t>Her hücredeki saat aralığını (örn. 19:20–20:05) doğrudan tıklayıp yazarak değiştirebilirsiniz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="43" t="inlineStr">
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="71" t="inlineStr">
+        <is>
+          <t>Her hücredeki saat aralığını doğrudan tıklayıp yazarak değiştirebilirsiniz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t>• Süreleri Yeniden Dengeleme</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>Bir bloğun süresini uzatmak isterseniz (örn. Ek Çalışmayı 1.5 saatten 2 saate çıkarmak), başka bir bloktan (mola, yemek veya dinlenme) o kadar dakika kısarak toplamı 270 dakikada sabit tutmanız gerekir; aksi halde 22:00 uyku hedefi kayar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="43" t="inlineStr">
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="71" t="inlineStr">
+        <is>
+          <t>Bir bloğun süresini uzatmak isterseniz başka bir bloktan o kadar dakika kısarak toplamı hafta içi için 270 dakikada (17:30-22:00), hafta sonu için 780 dakikada (09:00-22:00) sabit tutmanız gerekir; aksi halde 22:00 uyku hedefi kayar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="70" t="inlineStr">
+        <is>
+          <t>• Hafta Sonu Serbest Zaman</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="71" t="inlineStr">
+        <is>
+          <t>Cumartesi/Pazar'daki geniş 'Öğle + Serbest Zaman' ve 'Akşam + Serbest Zaman' blokları aile, hobi, spor gibi etkinlikler için ayrılmıştır; içeriğini dilediğiniz gibi değiştirebilirsiniz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="70" t="inlineStr">
         <is>
           <t>• Ek Çalışma İçeriği</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="44" t="inlineStr">
-        <is>
-          <t>"Ek Çalışma 1/2" satırlarındaki hücrelere dersin adını ve çalışma türünü (konu tekrarı, soru çözümü, test, yanlış analizi vb.) yazabilirsiniz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>• Uyku Saati</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="44" t="inlineStr">
-        <is>
-          <t>Program 22:00'de uyku hedefiyle tasarlanmıştır. Yatış saatini değiştirmek isterseniz son satırdaki "Yatış Hazırlığı" bloğunun saatini güncelleyip diğer blokları buna göre kaydırın.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>• Hafta İçi / Hafta Sonu</t>
-        </is>
-      </c>
-    </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="44" t="inlineStr">
-        <is>
-          <t>Program şu an tüm hafta için aynı saat şablonunu kullanır (tutarlı uyku düzeni için). Hafta sonu daha esnek olmasını isterseniz Cumartesi/Pazar sütunlarındaki saatleri ayrı ayrı değiştirebilirsiniz.</t>
+      <c r="A19" s="71" t="inlineStr">
+        <is>
+          <t>"Ek Çalışma 1/2" hücrelerine dersin adını ve çalışma türünü (konu tekrarı, soru çözümü, test, yanlış analizi vb.) yazabilirsiniz.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="70" t="inlineStr">
         <is>
           <t>• Renk Kodları</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="A22" s="71" t="inlineStr">
         <is>
           <t>Her blok türü farklı bir renkle gösterilir (bkz. sayfa üstündeki 'Renk Kodları' satırları).</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="70" t="inlineStr">
         <is>
           <t>• Logo Alanı</t>
         </is>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="44" t="inlineStr">
+      <c r="A25" s="71" t="inlineStr">
         <is>
           <t>Sol üst köşedeki gri kutu TED okul logosu için ayrılmıştır. Logo görseli temin edildiğinde Ekle &gt; Resim ile bu alana yerleştirilebilir.</t>
         </is>

--- a/7_Sinif_Haftalik_Ders_Calisma_Programi.xlsx
+++ b/7_Sinif_Haftalik_Ders_Calisma_Programi.xlsx
@@ -160,6 +160,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="0000695C"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="001A237E"/>
       <sz val="9.5"/>
     </font>
@@ -197,11 +202,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="0000695C"/>
-      <sz val="9.5"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="006D1F35"/>
       <sz val="9.5"/>
@@ -226,13 +226,30 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0000695C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A237E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00455A64"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00BF360C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00455A64"/>
+      <color rgb="005C5041"/>
       <sz val="10"/>
     </font>
     <font>
@@ -243,23 +260,6 @@
     <font>
       <name val="Arial"/>
       <color rgb="001B5E20"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001A237E"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="005C5041"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0000695C"/>
       <sz val="10"/>
     </font>
     <font>
@@ -538,28 +538,28 @@
     <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -576,34 +576,34 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="42" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1232,286 +1232,286 @@
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="29" t="inlineStr">
         <is>
-          <t>Günlük Ödev</t>
+          <t>Günlük Tekrar</t>
         </is>
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
           <t>18:30–19:15
-Günlük Ödevler</t>
+Günlük Tekrar
+(Bugünkü konuların özeti)</t>
         </is>
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
           <t>18:30–19:15
-Günlük Ödevler</t>
+Günlük Tekrar
+(Bugünkü konuların özeti)</t>
         </is>
       </c>
       <c r="D9" s="31" t="inlineStr">
         <is>
           <t>18:30–19:15
-Günlük Ödevler</t>
+Günlük Tekrar
+(Bugünkü konuların özeti)</t>
         </is>
       </c>
       <c r="E9" s="31" t="inlineStr">
         <is>
           <t>18:30–19:15
-Günlük Ödevler</t>
+Günlük Tekrar
+(Bugünkü konuların özeti)</t>
         </is>
       </c>
       <c r="F9" s="31" t="inlineStr">
         <is>
           <t>18:30–19:15
-Günlük Ödevler</t>
+Günlük Tekrar
+(Bugünkü konuların özeti)</t>
         </is>
       </c>
       <c r="G9" s="28" t="inlineStr"/>
       <c r="H9" s="28" t="inlineStr"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>Mola</t>
+          <t>Günlük Ödev</t>
         </is>
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>19:15–19:20
-Mola</t>
+          <t>19:15–20:00
+Günlük Ödevler</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
-          <t>19:15–19:20
-Mola</t>
+          <t>19:15–20:00
+Günlük Ödevler</t>
         </is>
       </c>
       <c r="D10" s="32" t="inlineStr">
         <is>
-          <t>19:15–19:20
-Mola</t>
+          <t>19:15–20:00
+Günlük Ödevler</t>
         </is>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
-          <t>19:15–19:20
-Mola</t>
+          <t>19:15–20:00
+Günlük Ödevler</t>
         </is>
       </c>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>19:15–19:20
-Mola</t>
+          <t>19:15–20:00
+Günlük Ödevler</t>
         </is>
       </c>
       <c r="G10" s="28" t="inlineStr"/>
       <c r="H10" s="28" t="inlineStr"/>
     </row>
-    <row r="11" ht="52" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="A11" s="29" t="inlineStr">
         <is>
+          <t>Mola</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>20:00–20:05
+Mola</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>20:00–20:05
+Mola</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>20:00–20:05
+Mola</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>20:00–20:05
+Mola</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>20:00–20:05
+Mola</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr"/>
+      <c r="H11" s="28" t="inlineStr"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
           <t>Ek Çalışma 1</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
-        <is>
-          <t>19:20–20:00
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>20:05–20:45
 Matematik
 Konu Tekrarı</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t>19:20–20:00
+      <c r="C12" s="35" t="inlineStr">
+        <is>
+          <t>20:05–20:45
 Türkçe
 Konu Tekrarı</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
-        <is>
-          <t>19:20–20:00
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>20:05–20:45
 Matematik
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="E11" s="34" t="inlineStr">
-        <is>
-          <t>19:20–20:00
+      <c r="E12" s="35" t="inlineStr">
+        <is>
+          <t>20:05–20:45
 Türkçe
 Konu Tekrarı</t>
         </is>
       </c>
-      <c r="F11" s="35" t="inlineStr">
-        <is>
-          <t>19:20–20:00
+      <c r="F12" s="36" t="inlineStr">
+        <is>
+          <t>20:05–20:45
 Fen Bilimleri
 Test Çözümü</t>
         </is>
       </c>
-      <c r="G11" s="28" t="inlineStr"/>
-      <c r="H11" s="28" t="inlineStr"/>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>Yemek</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>20:00–20:15
-Yemek</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>20:00–20:15
-Yemek</t>
-        </is>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
-        <is>
-          <t>20:00–20:15
-Yemek</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>20:00–20:15
-Yemek</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>20:00–20:15
-Yemek</t>
-        </is>
-      </c>
       <c r="G12" s="28" t="inlineStr"/>
       <c r="H12" s="28" t="inlineStr"/>
     </row>
-    <row r="13" ht="52" customHeight="1">
+    <row r="13" ht="44" customHeight="1">
       <c r="A13" s="29" t="inlineStr">
         <is>
+          <t>Yemek</t>
+        </is>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>20:45–21:00
+Yemek</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>20:45–21:00
+Yemek</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>20:45–21:00
+Yemek</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>20:45–21:00
+Yemek</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>20:45–21:00
+Yemek</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="inlineStr"/>
+      <c r="H13" s="28" t="inlineStr"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
           <t>Ek Çalışma 2</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>20:15–20:50
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>21:00–21:35
 Türkçe
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>20:15–20:50
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>21:00–21:35
 Matematik
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="D13" s="35" t="inlineStr">
-        <is>
-          <t>20:15–20:50
+      <c r="D14" s="36" t="inlineStr">
+        <is>
+          <t>21:00–21:35
 Fen Bilimleri
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="E13" s="37" t="inlineStr">
-        <is>
-          <t>20:15–20:50
+      <c r="E14" s="38" t="inlineStr">
+        <is>
+          <t>21:00–21:35
 Sosyal Bilgiler
 Soru Çözümü</t>
         </is>
       </c>
-      <c r="F13" s="34" t="inlineStr">
-        <is>
-          <t>20:15–20:50
+      <c r="F14" s="35" t="inlineStr">
+        <is>
+          <t>21:00–21:35
 Türkçe
 Test Çözümü</t>
         </is>
       </c>
-      <c r="G13" s="28" t="inlineStr"/>
-      <c r="H13" s="28" t="inlineStr"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>Mola</t>
-        </is>
-      </c>
-      <c r="B14" s="32" t="inlineStr">
-        <is>
-          <t>20:50–20:55
-Mola</t>
-        </is>
-      </c>
-      <c r="C14" s="32" t="inlineStr">
-        <is>
-          <t>20:50–20:55
-Mola</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>20:50–20:55
-Mola</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t>20:50–20:55
-Mola</t>
-        </is>
-      </c>
-      <c r="F14" s="32" t="inlineStr">
-        <is>
-          <t>20:50–20:55
-Mola</t>
-        </is>
-      </c>
       <c r="G14" s="28" t="inlineStr"/>
       <c r="H14" s="28" t="inlineStr"/>
     </row>
-    <row r="15" ht="44" customHeight="1">
+    <row r="15" ht="20" customHeight="1">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>Günlük Tekrar</t>
-        </is>
-      </c>
-      <c r="B15" s="38" t="inlineStr">
-        <is>
-          <t>20:55–21:40
-Günlük Tekrar
-(Bugünkü konuların özeti)</t>
-        </is>
-      </c>
-      <c r="C15" s="38" t="inlineStr">
-        <is>
-          <t>20:55–21:40
-Günlük Tekrar
-(Bugünkü konuların özeti)</t>
-        </is>
-      </c>
-      <c r="D15" s="38" t="inlineStr">
-        <is>
-          <t>20:55–21:40
-Günlük Tekrar
-(Bugünkü konuların özeti)</t>
-        </is>
-      </c>
-      <c r="E15" s="38" t="inlineStr">
-        <is>
-          <t>20:55–21:40
-Günlük Tekrar
-(Bugünkü konuların özeti)</t>
-        </is>
-      </c>
-      <c r="F15" s="38" t="inlineStr">
-        <is>
-          <t>20:55–21:40
-Günlük Tekrar
-(Bugünkü konuların özeti)</t>
+          <t>Mola</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>21:35–21:40
+Mola</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>21:35–21:40
+Mola</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>21:35–21:40
+Mola</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>21:35–21:40
+Mola</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>21:35–21:40
+Mola</t>
         </is>
       </c>
       <c r="G15" s="28" t="inlineStr"/>
@@ -1660,17 +1660,16 @@
       <c r="G21" s="44" t="n"/>
       <c r="H21" s="28" t="inlineStr"/>
     </row>
-    <row r="22" ht="50" customHeight="1">
+    <row r="22" ht="40" customHeight="1">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>Ek Çalışma 1</t>
+          <t>Günlük Tekrar</t>
         </is>
       </c>
       <c r="B22" s="45" t="inlineStr">
         <is>
           <t>09:30–10:15
-Matematik
-Yanlış Analizi</t>
+Günlük Tekrar</t>
         </is>
       </c>
       <c r="C22" s="46" t="n"/>
@@ -1678,88 +1677,88 @@
       <c r="E22" s="45" t="inlineStr">
         <is>
           <t>09:30–10:15
-Matematik
-Genel Tekrar</t>
+Haftalık Genel
+Değerlendirme</t>
         </is>
       </c>
       <c r="F22" s="46" t="n"/>
       <c r="G22" s="46" t="n"/>
       <c r="H22" s="28" t="inlineStr"/>
     </row>
-    <row r="23" ht="20" customHeight="1">
+    <row r="23" ht="40" customHeight="1">
       <c r="A23" s="29" t="inlineStr">
         <is>
-          <t>Mola</t>
+          <t>Ödev / Proje</t>
         </is>
       </c>
       <c r="B23" s="47" t="inlineStr">
         <is>
-          <t>10:15–10:25
-Mola</t>
+          <t>10:15–11:00
+Günlük Ödev /
+Proje Çalışması</t>
         </is>
       </c>
       <c r="C23" s="48" t="n"/>
       <c r="D23" s="48" t="n"/>
       <c r="E23" s="47" t="inlineStr">
         <is>
-          <t>10:15–10:25
-Mola</t>
+          <t>10:15–11:00
+Haftaya Hazırlık
+(Çanta, Kıyafet vb.)</t>
         </is>
       </c>
       <c r="F23" s="48" t="n"/>
       <c r="G23" s="48" t="n"/>
       <c r="H23" s="28" t="inlineStr"/>
     </row>
-    <row r="24" ht="50" customHeight="1">
+    <row r="24" ht="20" customHeight="1">
       <c r="A24" s="29" t="inlineStr">
         <is>
-          <t>Ek Çalışma 2</t>
+          <t>Mola</t>
         </is>
       </c>
       <c r="B24" s="49" t="inlineStr">
         <is>
-          <t>10:25–11:10
-Sosyal Bilgiler
-Soru Çözümü</t>
+          <t>11:00–11:10
+Mola</t>
         </is>
       </c>
       <c r="C24" s="50" t="n"/>
       <c r="D24" s="50" t="n"/>
-      <c r="E24" s="51" t="inlineStr">
-        <is>
-          <t>10:25–11:10
-Fen Bil. &amp; Sosyal Bil.
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t>11:00–11:10
+Mola</t>
+        </is>
+      </c>
+      <c r="F24" s="50" t="n"/>
+      <c r="G24" s="50" t="n"/>
+      <c r="H24" s="28" t="inlineStr"/>
+    </row>
+    <row r="25" ht="50" customHeight="1">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>Ek Çalışma 1</t>
+        </is>
+      </c>
+      <c r="B25" s="51" t="inlineStr">
+        <is>
+          <t>11:10–11:55
+Matematik
+Yanlış Analizi</t>
+        </is>
+      </c>
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="51" t="inlineStr">
+        <is>
+          <t>11:10–11:55
+Matematik
 Genel Tekrar</t>
         </is>
       </c>
-      <c r="F24" s="52" t="n"/>
-      <c r="G24" s="52" t="n"/>
-      <c r="H24" s="28" t="inlineStr"/>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="29" t="inlineStr">
-        <is>
-          <t>Ödev / Proje</t>
-        </is>
-      </c>
-      <c r="B25" s="53" t="inlineStr">
-        <is>
-          <t>11:10–12:00
-Günlük Ödev /
-Proje Çalışması</t>
-        </is>
-      </c>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="54" t="n"/>
-      <c r="E25" s="53" t="inlineStr">
-        <is>
-          <t>11:10–12:00
-Haftaya Hazırlık
-(Çanta, Kıyafet vb.)</t>
-        </is>
-      </c>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
+      <c r="F25" s="52" t="n"/>
+      <c r="G25" s="52" t="n"/>
       <c r="H25" s="28" t="inlineStr"/>
     </row>
     <row r="26" ht="44" customHeight="1">
@@ -1768,47 +1767,48 @@
           <t>Öğle + Serbest Zaman</t>
         </is>
       </c>
-      <c r="B26" s="55" t="inlineStr">
-        <is>
-          <t>12:00–16:00
+      <c r="B26" s="53" t="inlineStr">
+        <is>
+          <t>11:55–15:55
 Öğle Yemeği +
 Serbest Zaman
 (Aile / Hobi / Spor)</t>
         </is>
       </c>
-      <c r="C26" s="56" t="n"/>
-      <c r="D26" s="56" t="n"/>
-      <c r="E26" s="55" t="inlineStr">
-        <is>
-          <t>12:00–16:00
+      <c r="C26" s="54" t="n"/>
+      <c r="D26" s="54" t="n"/>
+      <c r="E26" s="53" t="inlineStr">
+        <is>
+          <t>11:55–15:55
 Öğle Yemeği +
 Serbest Zaman
 (Aile / Hobi / Spor)</t>
         </is>
       </c>
-      <c r="F26" s="56" t="n"/>
-      <c r="G26" s="56" t="n"/>
+      <c r="F26" s="54" t="n"/>
+      <c r="G26" s="54" t="n"/>
       <c r="H26" s="28" t="inlineStr"/>
     </row>
-    <row r="27" ht="40" customHeight="1">
+    <row r="27" ht="50" customHeight="1">
       <c r="A27" s="29" t="inlineStr">
         <is>
-          <t>Günlük Tekrar</t>
-        </is>
-      </c>
-      <c r="B27" s="57" t="inlineStr">
-        <is>
-          <t>16:00–16:45
-Günlük Tekrar</t>
-        </is>
-      </c>
-      <c r="C27" s="58" t="n"/>
-      <c r="D27" s="58" t="n"/>
+          <t>Ek Çalışma 2</t>
+        </is>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t>15:55–16:40
+Sosyal Bilgiler
+Soru Çözümü</t>
+        </is>
+      </c>
+      <c r="C27" s="56" t="n"/>
+      <c r="D27" s="56" t="n"/>
       <c r="E27" s="57" t="inlineStr">
         <is>
-          <t>16:00–16:45
-Haftalık Genel
-Değerlendirme</t>
+          <t>15:55–16:40
+Fen Bil. &amp; Sosyal Bil.
+Genel Tekrar</t>
         </is>
       </c>
       <c r="F27" s="58" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B28" s="59" t="inlineStr">
         <is>
-          <t>16:45–17:15
+          <t>16:40–17:10
 Kitap Okuma</t>
         </is>
       </c>
@@ -1831,7 +1831,7 @@
       <c r="D28" s="60" t="n"/>
       <c r="E28" s="59" t="inlineStr">
         <is>
-          <t>16:45–17:15
+          <t>16:40–17:10
 Kitap Okuma</t>
         </is>
       </c>
@@ -1845,24 +1845,24 @@
           <t>Akşam + Serbest Zaman</t>
         </is>
       </c>
-      <c r="B29" s="55" t="inlineStr">
-        <is>
-          <t>17:15–21:30
+      <c r="B29" s="53" t="inlineStr">
+        <is>
+          <t>17:10–21:30
 Akşam Yemeği +
 Serbest Zaman / Aile</t>
         </is>
       </c>
-      <c r="C29" s="56" t="n"/>
-      <c r="D29" s="56" t="n"/>
-      <c r="E29" s="55" t="inlineStr">
-        <is>
-          <t>17:15–21:30
+      <c r="C29" s="54" t="n"/>
+      <c r="D29" s="54" t="n"/>
+      <c r="E29" s="53" t="inlineStr">
+        <is>
+          <t>17:10–21:30
 Akşam Yemeği +
 Serbest Zaman / Aile</t>
         </is>
       </c>
-      <c r="F29" s="56" t="n"/>
-      <c r="G29" s="56" t="n"/>
+      <c r="F29" s="54" t="n"/>
+      <c r="G29" s="54" t="n"/>
       <c r="H29" s="28" t="inlineStr"/>
     </row>
     <row r="30" ht="40" customHeight="1">
